--- a/data/trans_camb/P1419-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1419-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -1,19</t>
+          <t>-4,42; -1,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,68</t>
+          <t>-2,61; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,46</t>
+          <t>-1,44; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -1,09</t>
+          <t>-8,58; -1,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; -0,2</t>
+          <t>-8,06; -0,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,71</t>
+          <t>-4,39; 2,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -1,7</t>
+          <t>-5,27; -1,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,29</t>
+          <t>-4,0; 0,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,17</t>
+          <t>-1,81; 2,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,16%</t>
+          <t>-8,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,2</t>
+          <t>-100,0; -49,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 98,97</t>
+          <t>-70,3; 117,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 135,73</t>
+          <t>-38,64; 152,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,17; -12,44</t>
+          <t>-81,9; -15,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 6,05</t>
+          <t>-77,85; 5,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 47,2</t>
+          <t>-42,29; 49,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,48; -42,65</t>
+          <t>-85,68; -40,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,13; 10,89</t>
+          <t>-66,27; 9,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 61,84</t>
+          <t>-28,38; 64,19</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,21</t>
+          <t>-3,61; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,17</t>
+          <t>-3,51; 0,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,8</t>
+          <t>-1,52; 2,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,56</t>
+          <t>-4,92; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -1,04</t>
+          <t>-7,19; -0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 4,44</t>
+          <t>-1,62; 5,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,29</t>
+          <t>-3,63; 0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -0,9</t>
+          <t>-4,54; -0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,92</t>
+          <t>-0,9; 3,01</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,07; 40,39</t>
+          <t>-92,41; 35,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,67</t>
+          <t>-92,99; 61,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 215,67</t>
+          <t>-44,08; 217,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 55,01</t>
+          <t>-58,35; 48,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,81; -11,21</t>
+          <t>-83,23; -4,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 96,06</t>
+          <t>-20,61; 107,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,49; 9,73</t>
+          <t>-62,01; 11,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,95; -23,27</t>
+          <t>-82,46; -23,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 88,06</t>
+          <t>-16,38; 89,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>3,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,59</t>
+          <t>-4,24; -0,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,5</t>
+          <t>-3,5; 0,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,6</t>
+          <t>-0,31; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 1,29</t>
+          <t>-9,95; 1,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 5,49</t>
+          <t>-8,04; 5,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 14,02</t>
+          <t>-0,44; 13,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -0,29</t>
+          <t>-4,6; -0,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,07</t>
+          <t>-3,61; 1,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,67</t>
+          <t>1,44; 6,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,14; -13,11</t>
+          <t>-85,64; -8,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,5; 28,07</t>
+          <t>-73,43; 23,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,82; 116,16</t>
+          <t>-7,39; 177,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,17; 20,15</t>
+          <t>-64,53; 21,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 68,71</t>
+          <t>-54,29; 62,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 176,95</t>
+          <t>-4,08; 177,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -6,55</t>
+          <t>-65,57; -4,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 23,18</t>
+          <t>-53,59; 27,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 92,73</t>
+          <t>18,91; 159,35</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,45</t>
+          <t>-2,37; 0,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,42</t>
+          <t>-3,01; -0,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,75</t>
+          <t>0,76; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -1,58</t>
+          <t>-7,19; -1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; -3,09</t>
+          <t>-8,59; -3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 0,36</t>
+          <t>-3,39; 2,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,68</t>
+          <t>-3,54; -0,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; -1,69</t>
+          <t>-4,48; -1,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,21</t>
+          <t>0,11; 3,13</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,57%</t>
+          <t>-3,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 22,38</t>
+          <t>-63,91; 16,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,76; -14,73</t>
+          <t>-78,84; -21,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,04; 181,15</t>
+          <t>17,88; 165,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,74; -16,39</t>
+          <t>-59,69; -14,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,29; -33,8</t>
+          <t>-69,58; -35,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 3,44</t>
+          <t>-26,88; 28,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,69; -13,01</t>
+          <t>-53,34; -13,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -32,28</t>
+          <t>-68,09; -34,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 42,7</t>
+          <t>1,37; 61,26</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>-2,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,49; -2,04</t>
+          <t>-7,46; -2,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -0,99</t>
+          <t>-6,48; -1,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,69; -0,15</t>
+          <t>-6,17; -0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 3,87</t>
+          <t>-3,59; 3,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,45</t>
+          <t>-5,46; 1,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,1</t>
+          <t>2,01; 8,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,63</t>
+          <t>-4,02; 0,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,58</t>
+          <t>-5,37; -0,63</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,91</t>
+          <t>-0,45; 4,1</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-48,78%</t>
+          <t>-53,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-96,12; -50,51</t>
+          <t>-96,18; -51,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-85,27; -24,6</t>
+          <t>-83,7; -20,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,17; 4,25</t>
+          <t>-79,39; -7,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 49,62</t>
+          <t>-29,97; 44,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 18,14</t>
+          <t>-44,8; 16,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 87,53</t>
+          <t>14,87; 105,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 9,74</t>
+          <t>-41,54; 11,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,26; -8,38</t>
+          <t>-54,98; -8,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 57,16</t>
+          <t>-4,71; 61,54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>-4,01</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-3,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,39; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,77</t>
+          <t>-1,63; 0,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,23</t>
+          <t>-2,07; 0,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,84</t>
+          <t>-4,36; 1,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -3,38</t>
+          <t>-8,52; -3,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -1,15</t>
+          <t>-6,56; -1,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,58</t>
+          <t>-3,76; 0,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -2,79</t>
+          <t>-6,93; -2,99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,75; -1,65</t>
+          <t>-5,41; -1,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-66,82%</t>
+          <t>-64,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-28,48%</t>
+          <t>-30,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-33,0%</t>
+          <t>-33,34%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 7,4</t>
+          <t>-30,13; 9,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -28,87</t>
+          <t>-59,38; -28,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-43,44; -9,56</t>
+          <t>-44,41; -12,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 6,25</t>
+          <t>-32,54; 4,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,98; -29,69</t>
+          <t>-60,25; -31,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -16,39</t>
+          <t>-46,36; -16,41</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -1,11</t>
+          <t>-2,57; -1,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,75</t>
+          <t>-2,26; -0,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,47</t>
+          <t>0,11; 1,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,9</t>
+          <t>-3,78; -0,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -3,26</t>
+          <t>-6,12; -3,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,8</t>
+          <t>-1,26; 1,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -1,18</t>
+          <t>-2,88; -1,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -2,31</t>
+          <t>-3,91; -2,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,82</t>
+          <t>-0,37; 1,31</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-7,12%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-1,05%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-74,19; -41,6</t>
+          <t>-73,73; -42,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,12; -27,9</t>
+          <t>-64,43; -26,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 54,73</t>
+          <t>2,99; 70,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,17; -9,24</t>
+          <t>-32,91; -8,24</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -32,55</t>
+          <t>-51,89; -33,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 7,67</t>
+          <t>-10,54; 14,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,87; -17,73</t>
+          <t>-38,67; -19,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,1; -35,07</t>
+          <t>-52,58; -34,7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 12,05</t>
+          <t>-5,02; 19,99</t>
         </is>
       </c>
     </row>
